--- a/inst/apps/GreatPlainsBCGCalc/external/RMD/files/Requirements.xlsx
+++ b/inst/apps/GreatPlainsBCGCalc/external/RMD/files/Requirements.xlsx
@@ -1,33 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/GreatPlainsBCGCalc/inst/apps/GreatPlainsBCGCalc/external/RMD/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\GreatPlainsBCGCalc\inst\apps\GreatPlainsBCGCalc\external\RMD\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2397B59E-CFC2-4FC1-9863-5185E4ABE346}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FE7602-F805-49C9-AB62-1088343FA2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Req_metadata" sheetId="1" r:id="rId1"/>
     <sheet name="Fish_classes" sheetId="2" r:id="rId2"/>
     <sheet name="Bug_classes" sheetId="3" r:id="rId3"/>
+    <sheet name="NOTES" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="FileName">NOTES!$B$8</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Erik W. Leppo</author>
+  </authors>
+  <commentList>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{C5DAB5B7-8E5B-4384-AE40-552AFFBB3A78}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Erik W. Leppo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+This is a formula and changes automatically.  This is needed for the hyperlinks below.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="79">
   <si>
     <t>Index_Name</t>
   </si>
@@ -62,12 +111,6 @@
     <t>KS_Bugs_BCG</t>
   </si>
   <si>
-    <t>CIP_medium</t>
-  </si>
-  <si>
-    <t>Omernik ecoregion = Central Irregular Plains (CIP; 40), modeled median flow 10-100 CFS (Perry et al. 2004)</t>
-  </si>
-  <si>
     <t>MO_Bugs_BCG</t>
   </si>
   <si>
@@ -183,13 +226,100 @@
   </si>
   <si>
     <t>Number of individuals</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Median flow statistic (Perry et al. 2002) &gt; 100 CFS (cubic feet per second), summarized by KDHE CUSEGA. Covers all three Omernik ecoregions (Central Great Plains (CGP; 27), Western Corn Belt (WCBP; 47) and Central Irregular Plains (CIP; 40))</t>
+  </si>
+  <si>
+    <t>CGP_Medium</t>
+  </si>
+  <si>
+    <t>Omernik ecoregion = Central Great Plains (CGP; 27). Large size (median flow statistic (Perry et al. 2002) = 10-100 CFS (cubic feet per second), summarized by KDHE flow segment (CUSEGA))</t>
+  </si>
+  <si>
+    <t>CIP_Medium</t>
+  </si>
+  <si>
+    <t>Omernik ecoregion = Central Irregular Plains (CIP; 40). Medium size (median flow statistic (Perry et al. 2002) = 10-100 CFS (cubic feet per second), summarized by KDHE flow segment (CUSEGA))</t>
+  </si>
+  <si>
+    <t>WCBP_SmallMedium</t>
+  </si>
+  <si>
+    <t>Omernik ecoregion = Western Corn Belt (WCBP; 47). Small and medium size (median flow statistic (Perry et al. 2002) = 0.01-100 CFS (cubic feet per second), summarized by KDHE flow segment (CUSEGA))</t>
+  </si>
+  <si>
+    <t>OK_Bugs_BCG</t>
+  </si>
+  <si>
+    <t>Riffle100_ChiroC_CGP</t>
+  </si>
+  <si>
+    <t>Omernik ecoregion = Central Great Plains (CGP; 27). 100-count, riffle habitat, coarse-level Chironomidae (CHIRONOMINI, DIAMESINAE, ORTHOCLADIINAE, PRODIAMESINAE, PSEUDOCHIRONOMINI, TANYPODINAE, TANYTARSINI)</t>
+  </si>
+  <si>
+    <t>Riffle100_ChiroC_CIP</t>
+  </si>
+  <si>
+    <t>Omernik ecoregion = Central Irregular Plains (CIP; 40). 100-count, riffle habitat, coarse-level Chironomidae (CHIRONOMINI, DIAMESINAE, ORTHOCLADIINAE, PRODIAMESINAE, PSEUDOCHIRONOMINI, TANYPODINAE, TANYTARSINI)</t>
+  </si>
+  <si>
+    <t>Updated Bug_Classes per email, Jen 2026-07-06</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Specific Task</t>
+  </si>
+  <si>
+    <t>Erik.Leppo@tetratech.com</t>
+  </si>
+  <si>
+    <t>Path &amp; FileName</t>
+  </si>
+  <si>
+    <t>FileName:</t>
+  </si>
+  <si>
+    <t>TabName:</t>
+  </si>
+  <si>
+    <t>Description of Work</t>
+  </si>
+  <si>
+    <t>blah, blah, blah</t>
+  </si>
+  <si>
+    <t>Worksheet</t>
+  </si>
+  <si>
+    <t>Descriptions</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Description of work and other worksheets.</t>
+  </si>
+  <si>
+    <t>Sheet2</t>
+  </si>
+  <si>
+    <t>Sheet3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,8 +341,63 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,8 +416,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -255,11 +446,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -272,11 +488,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="5">
+    <cellStyle name="Heading 1 2" xfId="2" xr:uid="{E243649E-268E-4FEB-AD94-31C03C42A0FA}"/>
+    <cellStyle name="Heading 2 2" xfId="4" xr:uid="{9FA7FE17-08C8-4A27-89F2-552038B14FA7}"/>
+    <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{20E99089-24BC-412B-A296-9CF62EAF35B4}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Title 2" xfId="1" xr:uid="{189CC2E4-4022-4EDE-A684-D5D2F6E1C1A5}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -287,6 +533,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2DD3B3A1-9957-4959-974C-9053BB2A9958}" name="Table1" displayName="Table1" ref="A15:C18" totalsRowShown="0">
+  <autoFilter ref="A15:C18" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{54D5AE47-091C-4A3A-B9FB-32A63A3E73AC}" name="Worksheet"/>
+    <tableColumn id="2" xr3:uid="{4F93FEDA-7D22-446D-9402-22EBF90DCB8B}" name="Descriptions"/>
+    <tableColumn id="3" xr3:uid="{A95F6004-A6FA-4E15-B9A3-1CFFED98E1D5}" name="Link" dataDxfId="0">
+      <calculatedColumnFormula>HYPERLINK(FileName&amp;A16&amp;"!A1",A16)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -564,16 +824,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>2</v>
@@ -584,84 +844,84 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>37</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
         <v>40</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>43</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>49</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -692,46 +952,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF15F720-FD3D-4A8B-8270-DD8AEA852B9F}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -772,25 +1032,25 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -798,57 +1058,258 @@
         <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C14">
+    <sortCondition ref="A2:A14"/>
+    <sortCondition ref="B2:B14"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57FB8C01-9751-40F9-BA1C-229D1428B6F5}">
+  <sheetPr>
+    <tabColor theme="1" tint="0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="71.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="14" t="str">
+        <f ca="1">LEFT(CELL("filename",B7),FIND("]",CELL("filename",B7)))</f>
+        <v>C:\Users\Erik.Leppo\Documents\GitHub\GreatPlainsBCGCalc\inst\apps\GreatPlainsBCGCalc\external\RMD\files\[Requirements.xlsx]</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="14" t="str">
+        <f ca="1">MID(CELL("filename",B8),FIND("[",CELL("filename",B8)),(FIND("]",CELL("filename",B8))-FIND("[",CELL("filename",B8)))+1)</f>
+        <v>[Requirements.xlsx]</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="15" t="str">
+        <f ca="1">MID(CELL("filename",B9),FIND("]",CELL("filename",B9))+1,LEN(CELL("filename",B9))-FIND("]",CELL("filename",B9)))</f>
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="18" t="str">
+        <f ca="1">HYPERLINK(FileName&amp;A16&amp;"!A1",A16)</f>
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="19" t="str">
+        <f ca="1">HYPERLINK(FileName&amp;A17&amp;"!A1",A17)</f>
+        <v>Sheet2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="19" t="str">
+        <f ca="1">HYPERLINK(FileName&amp;A18&amp;"!A1",A18)</f>
+        <v>Sheet3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>46211</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B8" xr:uid="{CDD6586A-AFA2-4CF6-9FE5-57E9BE9A5F8F}">
+      <formula1>""</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{E6624627-07BB-4DCC-9CFC-A6FFD44B7FB4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="91" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;D&amp;CPage &amp;P of &amp;N&amp;R&amp;F</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
 </file>